--- a/docs/assets/3rdparty/source/icecream-flavours.xlsx
+++ b/docs/assets/3rdparty/source/icecream-flavours.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leskneebone/Projects/docs/docs/assets/3rdparty/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E77B6A6-EF1E-2747-94F9-6B6C7570481F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36C75B9-8D67-B04B-859A-D26A15127382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16600" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
+    <workbookView xWindow="1060" yWindow="1540" windowWidth="27640" windowHeight="16600" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Banana</t>
   </si>
@@ -86,15 +86,9 @@
     <t>Bubblegum</t>
   </si>
   <si>
-    <t>Butter Brickle was the registered trademark of a toffee ice cream flavoring and of a toffee-centered chocolate-covered candy bar similar to the Heath bar, introduced by the Blackstone Hotel in Omaha, Nebraska, in the 1920s. Alternately, it is often prepared and sold as butter vanilla-flavored ice cream with tiny flecks of butter toffee instead of chunks of Heath bar.</t>
-  </si>
-  <si>
     <t>Butterscotch</t>
   </si>
   <si>
-    <t>Butter pecan is a smooth vanilla ice cream with a slight buttery flavor, with pecans added.</t>
-  </si>
-  <si>
     <t>Cake batter</t>
   </si>
   <si>
@@ -182,73 +176,104 @@
     <t>Taro</t>
   </si>
   <si>
-    <t>Cherry - includes variations (e.g. Amaretto cherry, black cherry)</t>
-  </si>
-  <si>
-    <t>Lúcuma - a popular Peruvian ice cream flavor with an orange color and a sweet nutty taste</t>
-  </si>
-  <si>
-    <t>Moon mist - a blend of grape, banana, and blue raspberry (or sometimes bubblegum) flavors, popular in Atlantic Canada. The flavors are generally blended together to give a mist-like texture.</t>
-  </si>
-  <si>
-    <t>Raspberry ripple - consists of raspberry syrup injected into vanilla ice cream.</t>
-  </si>
-  <si>
-    <t>Tiger tail - a flavor popular in Canada, consisting of orange-flavored ice cream with swirls of black licorice</t>
-  </si>
-  <si>
-    <t>Biscuit Tortoni - an ice cream made with eggs and heavy cream, often containing chopped cherries or topped with minced almonds or crumbled macaroons</t>
-  </si>
-  <si>
-    <t>Blue moon - an ice cream flavor with bright blue coloring, available in the Upper Midwest of the United States</t>
-  </si>
-  <si>
-    <t>Chocolate chip - vanilla base, with chunks of solid chocolate. Declining in popularity in the 2020s. Sometimes chocolate ice cream was used, which was usually called "Chocolate chocolate chip"</t>
-  </si>
-  <si>
-    <t>Goody Goody Gum Drops - unique to New Zealand</t>
-  </si>
-  <si>
-    <t>Hokey pokey - a flavor of ice cream in New Zealand, consisting of plain vanilla ice cream with small, solid lumps of honeycomb toffee</t>
-  </si>
-  <si>
-    <t>Mint chocolate chip - composed of mint ice cream with small chocolate chips. In some cases the liqueur crème de menthe is used to provide the mint flavor, but in most cases peppermint or spearmint flavoring is used.</t>
-  </si>
-  <si>
-    <t>Neapolitan - composed of vanilla, chocolate and strawberry ice cream together side by side</t>
-  </si>
-  <si>
-    <t>Rocky road - although there are variations from the original flavor, it is traditionally composed of chocolate ice cream, nuts, and whole or diced marshmallows, or sometimes replaced with marshmallow creme, a more fluid version</t>
-  </si>
-  <si>
-    <t>Spumoni - a molded Italian ice cream made with layers of different colors and flavors, usually containing candied fruits and nuts.</t>
-  </si>
-  <si>
-    <t>Tramontana - composed of dark chocolate, white chocolate, dulce de leche and cookies.</t>
-  </si>
-  <si>
-    <t>Bacon - a modern invention, generally created by adding bacon to egg custard and freezing the mixture</t>
-  </si>
-  <si>
-    <t>Crab - a Japanese creation,it is described as having a sweet taste; the island of Hokkaido, Japan, is known for manufacturing it</t>
-  </si>
-  <si>
-    <t>Spundekäs - based on the German cream cheese of the same name</t>
-  </si>
-  <si>
-    <t>Ube (purple yam) - a popular ice cream flavor in the Philippines</t>
+    <t>FLAVOR NAMES</t>
+  </si>
+  <si>
+    <t>FRUIT FLAVORS</t>
+  </si>
+  <si>
+    <t>Cherry : includes variations (e.g. Amaretto cherry, black cherry)</t>
+  </si>
+  <si>
+    <t>Lúcuma : a popular Peruvian ice cream flavor with an orange color and a sweet nutty taste</t>
+  </si>
+  <si>
+    <t>Moon mist : a blend of grape, banana, and blue raspberry (or sometimes bubblegum) flavors, popular in Atlantic Canada. The flavors are generally blended together to give a mist-like texture.</t>
+  </si>
+  <si>
+    <t>Raspberry ripple : consists of raspberry syrup injected into vanilla ice cream.</t>
+  </si>
+  <si>
+    <t>Tiger tail : a flavor popular in Canada, consisting of orange-flavored ice cream with swirls of black licorice</t>
+  </si>
+  <si>
+    <t>CHOCOLATE, NUTS AND OTHER SWEETS</t>
+  </si>
+  <si>
+    <t>Biscuit Tortoni : an ice cream made with eggs and heavy cream, often containing chopped cherries or topped with minced almonds or crumbled macaroons</t>
+  </si>
+  <si>
+    <t>Blue moon : an ice cream flavor with bright blue coloring, available in the Upper Midwest of the United States</t>
+  </si>
+  <si>
+    <t>Butter Brickle : the registered trademark of a toffee ice cream flavoring and of a toffee-centered chocolate-covered candy bar similar to the Heath bar, introduced by the Blackstone Hotel in Omaha, Nebraska, in the 1920s. Alternately, it is often prepared and sold as butter vanilla-flavored ice cream with tiny flecks of butter toffee instead of chunks of Heath bar.</t>
+  </si>
+  <si>
+    <t>Butter pecan : a smooth vanilla ice cream with a slight buttery flavor, with pecans added.</t>
+  </si>
+  <si>
+    <t>Chocolate chip : vanilla base, with chunks of solid chocolate. Declining in popularity in the 2020s. Sometimes chocolate ice cream was used, which was usually called "Chocolate chocolate chip"</t>
+  </si>
+  <si>
+    <t>Goody Goody Gum Drops : unique to New Zealand</t>
+  </si>
+  <si>
+    <t>Hokey pokey : a flavor of ice cream in New Zealand, consisting of plain vanilla ice cream with small, solid lumps of honeycomb toffee</t>
+  </si>
+  <si>
+    <t>Mint chocolate chip : composed of mint ice cream with small chocolate chips. In some cases the liqueur crème de menthe is used to provide the mint flavor, but in most cases peppermint or spearmint flavoring is used.</t>
+  </si>
+  <si>
+    <t>Neapolitan : composed of vanilla, chocolate and strawberry ice cream together side by side</t>
+  </si>
+  <si>
+    <t>Rocky road : although there are variations from the original flavor, it is traditionally composed of chocolate ice cream, nuts, and whole or diced marshmallows, or sometimes replaced with marshmallow creme, a more fluid version</t>
+  </si>
+  <si>
+    <t>Spumoni : a molded Italian ice cream made with layers of different colors and flavors, usually containing candied fruits and nuts.</t>
+  </si>
+  <si>
+    <t>Tramontana : composed of dark chocolate, white chocolate, dulce de leche and cookies.</t>
+  </si>
+  <si>
+    <t>SAVORY FLAVORS</t>
+  </si>
+  <si>
+    <t>Bacon : a modern invention, generally created by adding bacon to egg custard and freezing the mixture</t>
+  </si>
+  <si>
+    <t>Crab : a Japanese creation,it is described as having a sweet taste; the island of Hokkaido, Japan, is known for manufacturing it</t>
+  </si>
+  <si>
+    <t>Spundekas : based on the German cream cheese of the same name</t>
+  </si>
+  <si>
+    <t>Ube (purple yam) : a popular ice cream flavor in the Philippines</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -272,8 +297,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,342 +635,371 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" s="2"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>66</v>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assets/3rdparty/source/icecream-flavours.xlsx
+++ b/docs/assets/3rdparty/source/icecream-flavours.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leskneebone/Projects/docs/docs/assets/3rdparty/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36C75B9-8D67-B04B-859A-D26A15127382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B407A4FA-FC2B-164F-981C-FDBB8F5ACE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="1540" windowWidth="27640" windowHeight="16600" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
+    <workbookView xWindow="240" yWindow="740" windowWidth="27640" windowHeight="16600" xr2:uid="{D8F5B238-1CA9-2345-B0A6-1E95D04ABAF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -637,6 +637,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FF9460-F418-CA44-84AF-DE772B3A7DA8}">
   <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="94" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
